--- a/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
   <si>
     <t>BRDCY</t>
   </si>
@@ -656,168 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -854,86 +858,89 @@
       <c r="N8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="3">
         <v>8045300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6957900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6708500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5916300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5800300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5820400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5756600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5156000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5065500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5774300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4752500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6217800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8048800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8122100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8168200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8151300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9212700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8349700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8322400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7816100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8862300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>8318900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>8054200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7556300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>7913900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>7080300</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -970,86 +977,89 @@
       <c r="N9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9" s="3">
         <v>4924000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4264200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4114800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3615000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3318300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3396300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3395600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3069100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2818700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3709400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3230500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3894700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5024300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4951200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5149100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5094700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5770100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5275700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5136800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4767700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>5507100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>5290700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4957100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4610500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4741000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>4175500</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1086,86 +1096,89 @@
       <c r="N10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P10" s="3">
         <v>3121400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2693700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2593700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2301300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2482000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2424100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2361000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2086900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2246800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2064900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1522000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2323200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3024500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3170900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3019100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3056600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3442500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3074000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3185600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3048400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3355200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3028200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3097100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2945800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3172900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2904900</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1206,8 +1219,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1244,86 +1258,89 @@
       <c r="N12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P12" s="3">
         <v>216200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>179000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>184100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>175100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>157300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>163000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>168300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>159200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>126200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>173000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>186300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>229200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>252500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>235800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>252200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>243000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>269400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>238200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>228100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>220800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>241900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>216700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>232200</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>207300</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>215600</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>204000</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1438,8 +1455,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1476,86 +1496,89 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3">
         <v>36300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>12700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>5600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>85700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>49900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>26900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>39800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>12600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>487000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>682000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>383400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>47500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>190200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>41600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>100300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-103500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-280400</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>99800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>6400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>9300</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>58400</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>39200</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>95700</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1592,86 +1615,89 @@
       <c r="N15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="3">
         <v>187900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>173000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>165700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>154300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>158200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>161700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>161900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>156500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>159000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>171800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>179100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>193000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>312700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>310900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>200000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>203500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>85000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>84700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>79500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>78600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>80500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>76300</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>73000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>72800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>71300</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1709,8 +1735,9 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1747,86 +1774,89 @@
       <c r="N17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P17" s="3">
         <v>7093500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6107900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6126500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5334400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5037600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5098300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5071600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4565000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4771800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5669200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5164900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5873400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7408900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6921500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7573700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7348300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8154600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7219900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7417600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6908000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7883500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>7444900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>7166000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6700500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>6887600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>6189800</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1863,86 +1893,89 @@
       <c r="N18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P18" s="3">
         <v>951900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>850100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>582100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>581900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>762800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>722100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>684900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>591000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>293700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>105100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-412500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>344400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>640000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1200600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>594400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>803000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1058100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1129800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>904800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>908100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>978800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>874100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>888200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>855800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1026300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>890500</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1983,8 +2016,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2021,86 +2055,89 @@
       <c r="N20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P20" s="3">
         <v>-77100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-33000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>25800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>56400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>32100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>13800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>17500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>23500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>9400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-23300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>76900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>12700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>18700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>6000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>109100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-24800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>19900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-33000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>231400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>77600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>25400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-36800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>47400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2137,86 +2174,89 @@
       <c r="N21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P21" s="3">
         <v>1390000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1299100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1068500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1074100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1239400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1197600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1145300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1050200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>795700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>631400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>129400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>909400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1339200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1831800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1238200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1442400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1646500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1608300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1369100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1340400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1700000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1425200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1353700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1259500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1502500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1297500</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2253,86 +2293,89 @@
       <c r="N22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="3">
         <v>28800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>25000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>21100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>20100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>20900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>31800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>32800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>57400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>59900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>66700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>59900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>27700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>34100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>31600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>38200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>24500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>28500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>17900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>19500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2369,86 +2412,89 @@
       <c r="N23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P23" s="3">
         <v>846000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>792000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>586800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>618200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>773800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>715000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>683500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>596000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>278300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>90600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-467600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>287500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>659500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1153400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>546500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>749100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1142600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1077300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>890600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>843500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1172000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>927100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>885100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>801000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1054200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>848500</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2485,86 +2531,89 @@
       <c r="N24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P24" s="3">
         <v>212800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>144600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>224100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>176800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-25800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>178100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>172500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>130600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>123500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>154300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-54500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>117800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>184000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>311900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>138400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>192000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>447300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>269000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>226900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>242800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>331900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>307100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>212300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>255800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>298900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2679,8 +2728,11 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2717,86 +2769,89 @@
       <c r="N26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P26" s="3">
         <v>633200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>647400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>362700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>441400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>799600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>536900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>511000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>465400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>154800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-63700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-413100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>169800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>475500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>841500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>408100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>557100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>695400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>808300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>663700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>600600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>840100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>620100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>672800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>545200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>755300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>549900</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2833,86 +2888,89 @@
       <c r="N27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P27" s="3">
         <v>626600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>635400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>351700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>434400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>789800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>527900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>500500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>448400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>148300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-76400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-400700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>147700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>469700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>825800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>393100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>536100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>681400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>788200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>647300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>576300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>818200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>596000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>656300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>525400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>731700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3027,8 +3085,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3065,50 +3126,50 @@
       <c r="N29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P29" s="3">
         <v>165500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-88100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-76900</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-987700</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-19400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-7500</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>1574000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-142300</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>60300</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>46600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>23900</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3143,8 +3204,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3259,8 +3323,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3375,8 +3442,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3413,86 +3483,89 @@
       <c r="N32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P32" s="3">
         <v>77100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>33000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-25800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-56400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-32100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-13800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-17500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-23500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>23300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>24000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-76900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-12700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-18700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-109100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>24800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>33000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-231400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-77600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-25400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>36800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3529,86 +3602,89 @@
       <c r="N33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P33" s="3">
         <v>792100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>611200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>263600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>357500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-197900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>508500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>493000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2022400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-354100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>171600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>469700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>825800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>393100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>536100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>681400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>788200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>647300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>576300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>818200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>596000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>656300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>525400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>731700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3723,8 +3799,11 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3761,207 +3840,213 @@
       <c r="N35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="3">
         <v>792100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>611200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>263600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>357500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-197900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>508500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>493000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2022400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-354100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>171600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>469700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>825800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>393100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>536100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>681400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>788200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>647300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>576300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>818200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>596000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>656300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>525400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>731700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4002,8 +4087,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4044,124 +4130,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4870900</v>
+      </c>
+      <c r="E41" s="3">
         <v>4552700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4788600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4495200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4035300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4377200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5140400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4316800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4215700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4316800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4215700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3889200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3684200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3346700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4182100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4506600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5410400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6130200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7004500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8436200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5941300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5150000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5362800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3123800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3943900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2740700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3982700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3636300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4157200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3618500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3839700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3842000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4627500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3814400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4267500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3099000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4284300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3141800</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4199,897 +4289,921 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>107300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>146200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>63000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>65700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>80900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>54100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>51600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>45100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>53300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>51500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>86200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>155300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1369700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1356600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1323100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1240800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1452400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1538000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1440600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1170800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>2004000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1762800</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1563400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1328400</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1487500</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1346800</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6999500</v>
+      </c>
+      <c r="E43" s="3">
         <v>7263300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6827800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6917300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6600300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6486700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7081000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6943800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6937100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6943800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6937100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7074300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6720900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6234400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5941600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5292500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5094900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5021400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4848000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4560700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4894700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5247200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5166800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5957200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>11999600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5330100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5120200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5535200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5472300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5235300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4915100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4979300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4396600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4227700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3849600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3759800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3894300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3356000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5753700</v>
+      </c>
+      <c r="E44" s="3">
         <v>5647500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6356000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6012500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6290700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6231700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6161800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6525300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6833900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6525300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6833900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6939500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6285700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6016500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5727200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4807600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4329100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4487800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4166700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3725300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3600800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4021000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5073500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5496700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>11174200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5646400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5756300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6145500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5826700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>6012000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5542800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5444800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5335200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5557500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>5631700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>5198100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>4944200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>4617000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>984200</v>
+      </c>
+      <c r="E45" s="3">
         <v>493500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1423900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>422400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1110100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1049500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>388100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>989900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1070700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>989900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1070700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1093800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1041700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1030100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1232300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>911400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>836800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>635600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>649000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>587400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>569600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>679500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>648300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>643800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>780500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1290500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1233600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1217000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1145000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1780200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1605900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1554400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1599400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1782100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1801500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1521500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1552300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1529300</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18608200</v>
+      </c>
+      <c r="E46" s="3">
         <v>18261500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19396200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18214200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18036300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18145000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19135900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18775800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19057400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18775800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>19057400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18996800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>17839800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16774000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>17146200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15583800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15752000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16329200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16719800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17354700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15059700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15149100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16337500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>15376800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17476700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16364300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17415900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17774800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>18053400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>18184000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>17344100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>16991400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>17962800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>17144600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>17113800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>14906800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>16162500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>13990900</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1488600</v>
+      </c>
+      <c r="E47" s="3">
         <v>1464500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1450900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1469900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1675400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1754900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1658200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1527400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1458100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1527400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1458100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1613300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1018200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>991400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1107900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1065600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1137000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1145100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1145500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1050000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1009800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1054200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1276800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1505300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2990000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1752500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1842600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2137000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2062100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2715400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2197500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2397300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2506000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2589900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2498300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2378500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2322300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2025500</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13330100</v>
+      </c>
+      <c r="E48" s="3">
         <v>13846900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14004200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13795100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13743900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14035000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14597100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13522800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13776800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13522800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13776800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13997300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13191400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11939700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12426800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11674800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11829900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12035900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12457000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12007200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12331000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13384700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>15078000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>15667800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>31118800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13721000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13711500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>14610900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13861400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13471900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12947700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12817300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>13316300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12869100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12797900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>12444100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>12853700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>11547300</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2259300</v>
+      </c>
+      <c r="E49" s="3">
         <v>2355800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2464300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2314700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2405800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2459600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2489000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2358800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2276000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2358800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2276000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2295100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2103900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1948300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1972300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1826000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1787000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1807800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1487700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1428300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1576900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1642100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1787900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1829400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3799400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1743200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1768700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>861500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>957700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>954200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>903400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>891800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>949500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>992600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>988400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>656000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>657700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>570300</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5204,8 +5318,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5320,19 +5437,22 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>10</v>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -5343,101 +5463,104 @@
       <c r="I52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="J52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>1078400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1084900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1110900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>994800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>923600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>785600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>797700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>746000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>730400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>798900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>893400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>901800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1805500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1353500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1388500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1458400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1317400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1118100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1054100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1038900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1055100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1022800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>998600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>934800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>965000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>942100</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5552,124 +5675,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36315800</v>
+      </c>
+      <c r="E54" s="3">
         <v>36659100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37990700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36404500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36463500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36966900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>38505500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36895700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37288300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36895700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>37288300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>37574600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35231600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32738300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>33764200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31145100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31429500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32103700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32607800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32586200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>30707800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32029000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35373500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>35281000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>38963600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>34934500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>36127200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>36842700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>36252100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>36443600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>34446800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>34136600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>35789700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>34619000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>34397000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>31320200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>32961200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>29076100</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5710,8 +5839,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5752,704 +5882,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3520000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3831000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3510700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3884400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3727700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3708000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4251100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3580400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3653900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3580400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3653900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3864900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4313200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3627300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3655800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3255900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3551900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3032400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3076400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2733400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3079600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2599700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2589600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3128200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5968100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1835100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2026300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2185100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2208700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2243400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2116200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1950300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2103600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2025600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2021500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1854200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1735000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1541900</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>913100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1044900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1315100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1306800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1318000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1995700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2265700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2267800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2324600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2267800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2324600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1638200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1929500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1139600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1039500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1302700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1407200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1552700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1560400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2710100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2550400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2969700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3632300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1617000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2949000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1745500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2089300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2235600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2774400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2216500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1276800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1618000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1434900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1467800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1607300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1067600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3107800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1596600</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2238900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1713000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2725400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1825900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2489000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2403000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1971100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2810500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2626300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2810500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2626300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2624300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2232300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2532900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2690700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2342100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2071700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2121400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2131300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2479300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2006000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2082500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1936300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2027200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6356000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3969500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4052700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4241900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4382200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3976300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3814200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3884900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4692900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4226900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3933500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3658000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>4252700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3205600</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6671900</v>
+      </c>
+      <c r="E60" s="3">
         <v>7124400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7551300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7471700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7534600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8106600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8965200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8658600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8604800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8658600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8604800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8127400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7709200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7299800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7386100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6900800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7030800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6706400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6768200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7922700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7636000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7651900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8158200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6772400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8156500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7550100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8168300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8662700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8374400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8436100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7207200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7453300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8231300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7720400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7562300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>6579800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>7538000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>6344100</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4622700</v>
+      </c>
+      <c r="E61" s="3">
         <v>4229800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4198300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3321900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3354600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3474300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3623500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3445300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3520800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3445300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3520800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4397200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4283200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3957800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4174500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4008900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4165300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4321900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4445000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4555600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4825000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5152000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5627300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5787000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5978000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4133900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4137000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2442500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2031700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1989500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2684500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2665900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2714700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2646700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2640600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1438000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1481900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1404300</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>394700</v>
+      </c>
+      <c r="E62" s="3">
         <v>510200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>585100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>394000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>410000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>416600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>450000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>428800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>460400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>428800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>460400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>448000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1850500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1753800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1952700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1847700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1853700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2048700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2108100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2041900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2155300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2277400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2570900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2755700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4777500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2594100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2650800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2918600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2848700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3083300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2898400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2955800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3122900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3026900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3025700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2934900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3133100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2861500</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6564,8 +6713,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6680,8 +6832,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6796,124 +6951,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12699400</v>
+      </c>
+      <c r="E66" s="3">
         <v>12933500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13470300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12320500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12515000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13243900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14347300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13816000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13955500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13816000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13955500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14444400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14174200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13321000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13840300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13072000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13362200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13379600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13639700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14844900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14948600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15423000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16749200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15745300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>17560800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14744100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15439800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14541300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13766400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13999700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13266900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13552900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>14583900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13891000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>13721500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>11424400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>12677000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>11064600</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6954,8 +7115,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7070,8 +7232,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7186,8 +7351,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7302,8 +7470,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7418,124 +7589,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17952900</v>
+      </c>
+      <c r="E72" s="3">
         <v>19478200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20217500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18247200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17674400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18047000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19233700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>17720300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18197900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17720300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18197900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19034300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17756600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15202300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15804000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15308800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15874300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>16784800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>17007300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15925300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14682900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15438900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>17177700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18111900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>44028300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>22532700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>22193000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22722500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>22336800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>21311700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>20630000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>19983000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>21211900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>20394100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>20283300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>19252000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>19213200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>18542900</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7650,8 +7827,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7766,8 +7946,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7882,124 +8065,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23264600</v>
+      </c>
+      <c r="E76" s="3">
         <v>23355100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24161100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23734900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23626800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23374600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23790800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22735600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22987500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22735600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22987500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22760000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21057400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19417300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19923900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18073100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18067300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18724100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18968100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17741300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15759200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16606100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>18624400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>19535800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>21402800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20190400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20687400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>22301400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>22485700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>22443800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>21179900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20583800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>21205800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>20728000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>20675500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>19895800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>20284200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>18011600</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8114,129 +8303,135 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8273,86 +8468,89 @@
       <c r="N81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P81" s="3">
         <v>792100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>611200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>263600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>357500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-197900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>508500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>493000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2022400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-354100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>171600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>469700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>825800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>393100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>536100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>681400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>788200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>647300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>576300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>818200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>596000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>656300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>525400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>731700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8393,124 +8591,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>544700</v>
+      </c>
+      <c r="E83" s="3">
         <v>562400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>555300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>541300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>514800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>543400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>550200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>522200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>503000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>522200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>503000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>540500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>515200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>482100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>460700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>435800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>444600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>461700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>442800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>435700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>498300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>516900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>565200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>589000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>627500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>642000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>648500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>644800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>479300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>503300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>444400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>465300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>489800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>473600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>440100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>440600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>428800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>425200</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8625,8 +8827,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8741,8 +8946,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8857,8 +9065,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8973,8 +9184,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9089,100 +9303,103 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>929200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1535100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>757200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1452500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>515700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>850100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1681000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1259200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>806300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1259200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>806300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>901400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1025800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>913600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>138100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>399400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>416000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>180000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>644200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1553400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1323100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>691700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>564600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1895100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>694900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>888100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1172900</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG89" s="3">
-        <v>0</v>
+      <c r="AG89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH89" s="3">
         <v>0</v>
@@ -9205,8 +9422,11 @@
       <c r="AN89" s="3">
         <v>0</v>
       </c>
+      <c r="AO89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9247,100 +9467,101 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-326200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-433600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-328000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-543800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-361100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-599100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-616800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-392100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-376300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-392100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-376300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-620900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-85398000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-55869000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-41907000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-71552000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-55048000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-45318000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-196600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-349000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-376900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-364000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-325900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-566700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-626200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-678600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-523100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-680800</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
+      <c r="AG91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
@@ -9363,8 +9584,11 @@
       <c r="AN91" s="3">
         <v>0</v>
       </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9479,8 +9703,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9595,100 +9822,103 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-235400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-312000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-293200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-511800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-645700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-695800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-476100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-334600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-476100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-334600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-602900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-430700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1035300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-276600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-491600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-352700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-598100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-175200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>2055000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-292400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-382600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-522200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-44100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-358100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1335900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-694000</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG94" s="3">
-        <v>0</v>
+      <c r="AG94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH94" s="3">
         <v>0</v>
@@ -9711,8 +9941,11 @@
       <c r="AN94" s="3">
         <v>0</v>
       </c>
+      <c r="AO94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9753,95 +9986,96 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E96" s="3">
         <v>600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>5900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>5100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>447300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>457700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>5500</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="M96" s="3" t="s">
         <v>10</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P96" s="3">
         <v>-700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-376900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-4100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-393400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-430900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-6100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-293600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-273700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-490000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-528100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-572200</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -9869,8 +10103,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9985,8 +10222,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10101,8 +10341,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10217,100 +10460,103 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-392200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>223300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-207900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-763600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-756300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-257000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-573600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-129200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-573600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-129200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-323900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-288400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-595700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-645100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-892400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-210100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-526400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1688400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-326200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-385600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-724900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1947000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-568400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-230900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1732100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1278300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1194800</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
+      <c r="AG100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH100" s="3">
         <v>0</v>
@@ -10333,100 +10579,103 @@
       <c r="AN100" s="3">
         <v>0</v>
       </c>
+      <c r="AO100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200400</v>
+      </c>
+      <c r="E101" s="3">
         <v>139900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-160500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>21500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>299400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>12100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-370400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>114100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>427100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>114100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>427100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>324900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-346800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>105400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>391200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>262000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>110000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-32400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-57400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>316500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>28100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-53300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>82200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-164300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>102700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-89500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-56300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>67800</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
+      <c r="AG101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH101" s="3">
         <v>0</v>
@@ -10449,100 +10698,103 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>850200</v>
+      </c>
+      <c r="E102" s="3">
         <v>1028100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>703400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>958500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-78600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-411900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>567700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>230900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>641900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>230900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>641900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-40200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-612000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-392400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-722700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-430700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-740900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1741100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2689400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1095400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>252500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2338300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-690300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1329100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1274100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>564100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-648100</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG102" s="3">
-        <v>0</v>
+      <c r="AG102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH102" s="3">
         <v>0</v>
@@ -10563,6 +10815,9 @@
         <v>0</v>
       </c>
       <c r="AN102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="3">
         <v>0</v>
       </c>
     </row>
